--- a/artfynd/A 11668-2026 artfynd.xlsx
+++ b/artfynd/A 11668-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131606728</v>
       </c>
       <c r="B2" t="n">
-        <v>57893</v>
+        <v>57895</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>131606991</v>
       </c>
       <c r="B3" t="n">
-        <v>57888</v>
+        <v>57890</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11668-2026 artfynd.xlsx
+++ b/artfynd/A 11668-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131606728</v>
       </c>
       <c r="B2" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>131606991</v>
       </c>
       <c r="B3" t="n">
-        <v>57890</v>
+        <v>57891</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11668-2026 artfynd.xlsx
+++ b/artfynd/A 11668-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131606728</v>
       </c>
       <c r="B2" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>131606991</v>
       </c>
       <c r="B3" t="n">
-        <v>57891</v>
+        <v>57894</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11668-2026 artfynd.xlsx
+++ b/artfynd/A 11668-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131606728</v>
       </c>
       <c r="B2" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>131606991</v>
       </c>
       <c r="B3" t="n">
-        <v>57894</v>
+        <v>57896</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11668-2026 artfynd.xlsx
+++ b/artfynd/A 11668-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131606728</v>
       </c>
       <c r="B2" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>131606991</v>
       </c>
       <c r="B3" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11668-2026 artfynd.xlsx
+++ b/artfynd/A 11668-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131606728</v>
       </c>
       <c r="B2" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>131606991</v>
       </c>
       <c r="B3" t="n">
-        <v>57899</v>
+        <v>57904</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11668-2026 artfynd.xlsx
+++ b/artfynd/A 11668-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131606728</v>
       </c>
       <c r="B2" t="n">
-        <v>57909</v>
+        <v>57911</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>131606991</v>
       </c>
       <c r="B3" t="n">
-        <v>57904</v>
+        <v>57906</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
